--- a/M2_Statistica_&_Excel/W2_D4.xlsx
+++ b/M2_Statistica_&_Excel/W2_D4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SZN\Desktop\EPICODE CORSO\esercizi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SZN\Desktop\EPICODE CORSO\esercizi\esercizi consegnati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07730A81-FC04-4C1C-98A6-34889841C38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDBF7875-15C9-4AA8-BE28-8D3A2D887B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Esercizo_p_value_sig" sheetId="2" r:id="rId1"/>
@@ -612,7 +612,7 @@
         <v>43</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15">
